--- a/stacked_model/results/candidates/bo_recommended_batch.xlsx
+++ b/stacked_model/results/candidates/bo_recommended_batch.xlsx
@@ -502,19 +502,19 @@
         <v>959.2222212006562</v>
       </c>
       <c r="F2" t="n">
-        <v>3.054853077716411</v>
+        <v>3.054853077716398</v>
       </c>
       <c r="G2" t="n">
         <v>4.911296439845443</v>
       </c>
       <c r="H2" t="n">
-        <v>90.6398084036133</v>
+        <v>90.63981244359209</v>
       </c>
       <c r="I2" t="n">
-        <v>6.124067204543739</v>
+        <v>5.958147515790889</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9119235665300374</v>
+        <v>0.9106270389875044</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -539,19 +539,19 @@
         <v>869.9800556580221</v>
       </c>
       <c r="F3" t="n">
-        <v>3.216924556757448</v>
+        <v>3.21692455675737</v>
       </c>
       <c r="G3" t="n">
-        <v>6.155618565168613</v>
+        <v>6.155618565168608</v>
       </c>
       <c r="H3" t="n">
-        <v>89.23878825724609</v>
+        <v>89.23876172168031</v>
       </c>
       <c r="I3" t="n">
-        <v>7.998983892860283</v>
+        <v>7.872709693123493</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8886431696535796</v>
+        <v>0.8887644873685224</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -576,19 +576,19 @@
         <v>904.1332685815627</v>
       </c>
       <c r="F4" t="n">
-        <v>3.558344109492031</v>
+        <v>3.558344109492017</v>
       </c>
       <c r="G4" t="n">
-        <v>5.69293320319801</v>
+        <v>5.692933203197999</v>
       </c>
       <c r="H4" t="n">
-        <v>89.69507944900516</v>
+        <v>89.69507785756146</v>
       </c>
       <c r="I4" t="n">
-        <v>7.118746306148844</v>
+        <v>6.976540199633475</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8876358172178144</v>
+        <v>0.8870268539411051</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -613,19 +613,19 @@
         <v>965.1252898393402</v>
       </c>
       <c r="F5" t="n">
-        <v>3.192407697790301</v>
+        <v>3.192407697790276</v>
       </c>
       <c r="G5" t="n">
         <v>5.120025599712179</v>
       </c>
       <c r="H5" t="n">
-        <v>90.16157638674404</v>
+        <v>90.16157747605344</v>
       </c>
       <c r="I5" t="n">
-        <v>6.015451432314511</v>
+        <v>5.846452015279758</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8816254683519393</v>
+        <v>0.8798325060809247</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
